--- a/04_Figures/F04_association/modules/T2/spearman/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T2/spearman/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.157142857142857</v>
+        <v>-0.0428571428571429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.573714526046661</v>
+        <v>-0.154665731331055</v>
       </c>
       <c r="F2" t="n">
-        <v>0.575952600603795</v>
+        <v>0.8794603130259</v>
       </c>
       <c r="G2" t="n">
-        <v>0.919489908382186</v>
+        <v>0.959699764598948</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0321428571428571</v>
+        <v>0.260714285714286</v>
       </c>
       <c r="E3" t="n">
-        <v>0.115952634048852</v>
+        <v>0.973692917115073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.909462117094591</v>
+        <v>0.347979459862794</v>
       </c>
       <c r="G3" t="n">
-        <v>0.919489908382186</v>
+        <v>0.848787679919784</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2</v>
+        <v>0.182142857142857</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.735980072193987</v>
+        <v>0.667897955721517</v>
       </c>
       <c r="F4" t="n">
-        <v>0.474813964522168</v>
+        <v>0.515881681707039</v>
       </c>
       <c r="G4" t="n">
-        <v>0.919489908382186</v>
+        <v>0.848787679919784</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.339285714285714</v>
+        <v>-0.110714285714286</v>
       </c>
       <c r="E5" t="n">
-        <v>1.30045037243686</v>
+        <v>-0.401655299909643</v>
       </c>
       <c r="F5" t="n">
-        <v>0.216028925341955</v>
+        <v>0.694462647207096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.919489908382186</v>
+        <v>0.848787679919784</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0857142857142857</v>
+        <v>-0.0142857142857143</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.310188821950692</v>
+        <v>-0.0515131320740328</v>
       </c>
       <c r="F6" t="n">
-        <v>0.761334126190767</v>
+        <v>0.959699764598948</v>
       </c>
       <c r="G6" t="n">
-        <v>0.919489908382186</v>
+        <v>0.959699764598948</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.075</v>
+        <v>0.121428571428571</v>
       </c>
       <c r="E7" t="n">
-        <v>0.271180115299783</v>
+        <v>0.441080862981928</v>
       </c>
       <c r="F7" t="n">
-        <v>0.790510794155268</v>
+        <v>0.66640111372339</v>
       </c>
       <c r="G7" t="n">
-        <v>0.919489908382186</v>
+        <v>0.848787679919784</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.235714285714286</v>
+        <v>0.139285714285714</v>
       </c>
       <c r="E8" t="n">
-        <v>0.874521871729162</v>
+        <v>0.507145317953373</v>
       </c>
       <c r="F8" t="n">
-        <v>0.397702945903273</v>
+        <v>0.620546087627901</v>
       </c>
       <c r="G8" t="n">
-        <v>0.919489908382186</v>
+        <v>0.848787679919784</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0464285714285714</v>
+        <v>0.217857142857143</v>
       </c>
       <c r="E9" t="n">
-        <v>0.16758131253873</v>
+        <v>0.804826493639811</v>
       </c>
       <c r="F9" t="n">
-        <v>0.869491525545095</v>
+        <v>0.435392673515538</v>
       </c>
       <c r="G9" t="n">
-        <v>0.919489908382186</v>
+        <v>0.848787679919784</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.167857142857143</v>
+        <v>0.164285714285714</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6139283620727</v>
+        <v>0.6004996783241</v>
       </c>
       <c r="F10" t="n">
-        <v>0.549855554227802</v>
+        <v>0.558497373248601</v>
       </c>
       <c r="G10" t="n">
-        <v>0.919489908382186</v>
+        <v>0.848787679919784</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0285714285714286</v>
+        <v>-0.125</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.103057823733474</v>
+        <v>-0.454256762579498</v>
       </c>
       <c r="F11" t="n">
-        <v>0.919489908382186</v>
+        <v>0.65713566818695</v>
       </c>
       <c r="G11" t="n">
-        <v>0.919489908382186</v>
+        <v>0.848787679919784</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.217857142857143</v>
+        <v>-0.271428571428571</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.804826493639811</v>
+        <v>-1.01682258925182</v>
       </c>
       <c r="F12" t="n">
-        <v>0.435392673515538</v>
+        <v>0.327789306841173</v>
       </c>
       <c r="G12" t="n">
-        <v>0.919489908382186</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.125</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.454256762579498</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.65713566818695</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.919489908382186</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0928571428571428</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.33625399478566</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.742045009907367</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.919489908382186</v>
+        <v>0.848787679919784</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.385714285714286</v>
+        <v>0.114285714285714</v>
       </c>
       <c r="E2" t="n">
-        <v>1.50735430417727</v>
+        <v>0.41478067789217</v>
       </c>
       <c r="F2" t="n">
-        <v>0.15563079458596</v>
+        <v>0.685065762656897</v>
       </c>
       <c r="G2" t="n">
-        <v>0.718937497327809</v>
+        <v>0.941965423653234</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0964285714285714</v>
+        <v>-0.0178571428571429</v>
       </c>
       <c r="E3" t="n">
-        <v>0.349305956924652</v>
+        <v>-0.064395112101152</v>
       </c>
       <c r="F3" t="n">
-        <v>0.732452863386731</v>
+        <v>0.949635304173862</v>
       </c>
       <c r="G3" t="n">
-        <v>0.845817431668134</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.114285714285714</v>
+        <v>0.196428571428571</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.41478067789217</v>
+        <v>0.72230513620243</v>
       </c>
       <c r="F4" t="n">
-        <v>0.685065762656897</v>
+        <v>0.482898756271634</v>
       </c>
       <c r="G4" t="n">
-        <v>0.845817431668134</v>
+        <v>0.823875422930297</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00714285714285714</v>
+        <v>-0.0785714285714286</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0257545946952327</v>
+        <v>-0.284171835544338</v>
       </c>
       <c r="F5" t="n">
-        <v>0.979844227761598</v>
+        <v>0.780754552309047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.979844227761598</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.135714285714286</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.493894317922737</v>
+        <v>0.735980072193987</v>
       </c>
       <c r="F6" t="n">
-        <v>0.629620441872815</v>
+        <v>0.474813964522168</v>
       </c>
       <c r="G6" t="n">
-        <v>0.845817431668134</v>
+        <v>0.823875422930297</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.182142857142857</v>
+        <v>0.339285714285714</v>
       </c>
       <c r="E7" t="n">
-        <v>0.667897955721517</v>
+        <v>1.30045037243686</v>
       </c>
       <c r="F7" t="n">
-        <v>0.515881681707039</v>
+        <v>0.216028925341955</v>
       </c>
       <c r="G7" t="n">
-        <v>0.845817431668134</v>
+        <v>0.823875422930297</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.442857142857143</v>
+        <v>0.314285714285714</v>
       </c>
       <c r="E8" t="n">
-        <v>1.78090346782642</v>
+        <v>1.19365775688834</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0982940655468714</v>
+        <v>0.253940016323672</v>
       </c>
       <c r="G8" t="n">
-        <v>0.718937497327809</v>
+        <v>0.823875422930297</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.335714285714286</v>
+        <v>0.310714285714286</v>
       </c>
       <c r="E9" t="n">
-        <v>1.28501221666837</v>
+        <v>1.17863475210372</v>
       </c>
       <c r="F9" t="n">
-        <v>0.221211537639326</v>
+        <v>0.259667397337218</v>
       </c>
       <c r="G9" t="n">
-        <v>0.718937497327809</v>
+        <v>0.823875422930297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.178571428571429</v>
+        <v>-0.025</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.654366100445603</v>
+        <v>-0.0901669634667432</v>
       </c>
       <c r="F10" t="n">
-        <v>0.524284360046553</v>
+        <v>0.929528970819238</v>
       </c>
       <c r="G10" t="n">
-        <v>0.845817431668134</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.125</v>
+        <v>-0.225</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.454256762579498</v>
+        <v>-0.832597876032085</v>
       </c>
       <c r="F11" t="n">
-        <v>0.65713566818695</v>
+        <v>0.420104686907635</v>
       </c>
       <c r="G11" t="n">
-        <v>0.845817431668134</v>
+        <v>0.823875422930297</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.339285714285714</v>
+        <v>-0.178571428571429</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.30045037243686</v>
+        <v>-0.654366100445603</v>
       </c>
       <c r="F12" t="n">
-        <v>0.216028925341955</v>
+        <v>0.524284360046553</v>
       </c>
       <c r="G12" t="n">
-        <v>0.718937497327809</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.196428571428571</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.72230513620243</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.482898756271634</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.845817431668134</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0785714285714286</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.284171835544338</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.780754552309047</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.845817431668134</v>
+        <v>0.823875422930297</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.271428571428571</v>
+        <v>0.0428571428571429</v>
       </c>
       <c r="E2" t="n">
-        <v>1.01682258925182</v>
+        <v>0.154665731331055</v>
       </c>
       <c r="F2" t="n">
-        <v>0.327789306841173</v>
+        <v>0.8794603130259</v>
       </c>
       <c r="G2" t="n">
-        <v>0.97717427255536</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00714285714285714</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0257545946952327</v>
+        <v>-0.258198889747161</v>
       </c>
       <c r="F3" t="n">
-        <v>0.979844227761598</v>
+        <v>0.800295987397054</v>
       </c>
       <c r="G3" t="n">
-        <v>0.979844227761598</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0892857142857143</v>
+        <v>0.0964285714285714</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.323215124514436</v>
+        <v>0.349305956924652</v>
       </c>
       <c r="F4" t="n">
-        <v>0.751672517350277</v>
+        <v>0.732452863386731</v>
       </c>
       <c r="G4" t="n">
-        <v>0.97717427255536</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0142857142857143</v>
+        <v>-0.0535714285714286</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0515131320740328</v>
+        <v>-0.193432297524523</v>
       </c>
       <c r="F5" t="n">
-        <v>0.959699764598948</v>
+        <v>0.849609936777607</v>
       </c>
       <c r="G5" t="n">
-        <v>0.979844227761598</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0571428571428571</v>
+        <v>0.125</v>
       </c>
       <c r="E6" t="n">
-        <v>0.206368705447417</v>
+        <v>0.454256762579498</v>
       </c>
       <c r="F6" t="n">
-        <v>0.839699868741576</v>
+        <v>0.65713566818695</v>
       </c>
       <c r="G6" t="n">
-        <v>0.979844227761598</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.107142857142857</v>
+        <v>0.228571428571429</v>
       </c>
       <c r="E7" t="n">
-        <v>0.38854567548164</v>
+        <v>0.846536236876207</v>
       </c>
       <c r="F7" t="n">
-        <v>0.703901001626162</v>
+        <v>0.41256617049636</v>
       </c>
       <c r="G7" t="n">
-        <v>0.97717427255536</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.332142857142857</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="n">
-        <v>1.26963651854388</v>
+        <v>1.13389341902768</v>
       </c>
       <c r="F8" t="n">
-        <v>0.226471759070724</v>
+        <v>0.277316780368384</v>
       </c>
       <c r="G8" t="n">
-        <v>0.97717427255536</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.35</v>
+        <v>0.167857142857143</v>
       </c>
       <c r="E9" t="n">
-        <v>1.34715062810913</v>
+        <v>0.6139283620727</v>
       </c>
       <c r="F9" t="n">
-        <v>0.200945350816293</v>
+        <v>0.549855554227802</v>
       </c>
       <c r="G9" t="n">
-        <v>0.97717427255536</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.153571428571429</v>
+        <v>-0.0464285714285714</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.560356865859059</v>
+        <v>-0.16758131253873</v>
       </c>
       <c r="F10" t="n">
-        <v>0.584764094941016</v>
+        <v>0.869491525545095</v>
       </c>
       <c r="G10" t="n">
-        <v>0.97717427255536</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.207142857142857</v>
+        <v>-0.110714285714286</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.763422283414352</v>
+        <v>-0.401655299909643</v>
       </c>
       <c r="F11" t="n">
-        <v>0.45884280496347</v>
+        <v>0.694462647207096</v>
       </c>
       <c r="G11" t="n">
-        <v>0.97717427255536</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3</v>
+        <v>-0.164285714285714</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.13389341902768</v>
+        <v>-0.6004996783241</v>
       </c>
       <c r="F12" t="n">
-        <v>0.277316780368384</v>
+        <v>0.558497373248601</v>
       </c>
       <c r="G12" t="n">
-        <v>0.97717427255536</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.114285714285714</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.41478067789217</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.685065762656897</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.97717427255536</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.167857142857143</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.6139283620727</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.549855554227802</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.97717427255536</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.560714285714286</v>
+        <v>-0.303571428571428</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.44161989115426</v>
+        <v>-1.14875354327913</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0296764960944747</v>
+        <v>0.271355836003868</v>
       </c>
       <c r="G2" t="n">
-        <v>0.113966645704307</v>
+        <v>0.497485699340426</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0571428571428571</v>
+        <v>0.803571428571428</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.206368705447417</v>
+        <v>4.8677376148421</v>
       </c>
       <c r="F3" t="n">
-        <v>0.839699868741576</v>
+        <v>0.000307265031812509</v>
       </c>
       <c r="G3" t="n">
-        <v>0.899446993472087</v>
+        <v>0.0033799153499376</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.35</v>
+        <v>0.210714285714286</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.34715062810913</v>
+        <v>0.777190891009981</v>
       </c>
       <c r="F4" t="n">
-        <v>0.200945350816293</v>
+        <v>0.450957865215285</v>
       </c>
       <c r="G4" t="n">
-        <v>0.351047003680676</v>
+        <v>0.708648073909734</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6.51664535375884</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0000195226138159411</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000253793979607234</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.546428571428571</v>
+        <v>-0.507142857142857</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.35243319092559</v>
+        <v>-2.12160364008743</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0350666602167099</v>
+        <v>0.0536636637808059</v>
       </c>
       <c r="G6" t="n">
-        <v>0.113966645704307</v>
+        <v>0.147575075397216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0357142857142857</v>
+        <v>-0.564285714285714</v>
       </c>
       <c r="E7" t="n">
-        <v>0.128851890580845</v>
+        <v>-2.46440336155382</v>
       </c>
       <c r="F7" t="n">
-        <v>0.899446993472087</v>
+        <v>0.0284325221487085</v>
       </c>
       <c r="G7" t="n">
-        <v>0.899446993472087</v>
+        <v>0.104252581211931</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.242857142857143</v>
+        <v>-0.157142857142857</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.90265758615802</v>
+        <v>-0.573714526046661</v>
       </c>
       <c r="F8" t="n">
-        <v>0.383128341839342</v>
+        <v>0.575952600603795</v>
       </c>
       <c r="G8" t="n">
-        <v>0.553407604879049</v>
+        <v>0.791934825830218</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.453571428571428</v>
+        <v>0.075</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.83498482509959</v>
+        <v>0.271180115299783</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0894859001430274</v>
+        <v>0.790510794155268</v>
       </c>
       <c r="G9" t="n">
-        <v>0.193886116976559</v>
+        <v>0.966179859523105</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0571428571428571</v>
+        <v>0.578571428571428</v>
       </c>
       <c r="E10" t="n">
-        <v>0.206368705447417</v>
+        <v>2.55761136070022</v>
       </c>
       <c r="F10" t="n">
-        <v>0.839699868741576</v>
+        <v>0.0238466587629967</v>
       </c>
       <c r="G10" t="n">
-        <v>0.899446993472087</v>
+        <v>0.104252581211931</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>-0.00357142857142857</v>
       </c>
       <c r="E11" t="n">
-        <v>2.08166599946613</v>
+        <v>-0.0128770509652542</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05769884126896</v>
+        <v>0.989921406880978</v>
       </c>
       <c r="G11" t="n">
-        <v>0.150016987299296</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.339285714285714</v>
+        <v>-0.332142857142857</v>
       </c>
       <c r="E12" t="n">
-        <v>1.30045037243686</v>
+        <v>-1.26963651854388</v>
       </c>
       <c r="F12" t="n">
-        <v>0.216028925341955</v>
+        <v>0.226471759070724</v>
       </c>
       <c r="G12" t="n">
-        <v>0.351047003680676</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0357142857142857</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.128851890580845</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.899446993472087</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.899446993472087</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.571428571428571</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.51058365784339</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.0260631933763629</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.113966645704307</v>
+        <v>0.497485699340426</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.057399680266734</v>
+        <v>0.480722322233897</v>
       </c>
       <c r="E2" t="n">
-        <v>0.207299269010996</v>
+        <v>1.97664795003352</v>
       </c>
       <c r="F2" t="n">
-        <v>0.838988074179233</v>
+        <v>0.0696896939656278</v>
       </c>
       <c r="G2" t="n">
-        <v>0.838988074179233</v>
+        <v>0.278310804433051</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.597315422775701</v>
+        <v>-0.218836281016923</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6853293824561</v>
+        <v>-0.808625221124944</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0187099304025155</v>
+        <v>0.433280499152867</v>
       </c>
       <c r="G3" t="n">
-        <v>0.149996727713314</v>
+        <v>0.622628985316801</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0986557004584491</v>
+        <v>0.313904501458702</v>
       </c>
       <c r="E4" t="n">
-        <v>0.357451970618205</v>
+        <v>1.19205154385119</v>
       </c>
       <c r="F4" t="n">
-        <v>0.726489691659864</v>
+        <v>0.254547639665085</v>
       </c>
       <c r="G4" t="n">
-        <v>0.838988074179233</v>
+        <v>0.560004807263186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.211661320983582</v>
+        <v>0.209867580975246</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.780847346013662</v>
+        <v>0.773923746376168</v>
       </c>
       <c r="F5" t="n">
-        <v>0.448878397284934</v>
+        <v>0.452821080230401</v>
       </c>
       <c r="G5" t="n">
-        <v>0.729427395588018</v>
+        <v>0.622628985316801</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.355160521650417</v>
+        <v>0.469959882183885</v>
       </c>
       <c r="E6" t="n">
-        <v>1.36985683710535</v>
+        <v>1.91966457395886</v>
       </c>
       <c r="F6" t="n">
-        <v>0.193927844959291</v>
+        <v>0.0771157713366422</v>
       </c>
       <c r="G6" t="n">
-        <v>0.504212396894158</v>
+        <v>0.278310804433051</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0753370803500884</v>
+        <v>0.0143499200666835</v>
       </c>
       <c r="E7" t="n">
-        <v>0.272405849783859</v>
+        <v>0.0517447005132249</v>
       </c>
       <c r="F7" t="n">
-        <v>0.789588717980595</v>
+        <v>0.959518775459607</v>
       </c>
       <c r="G7" t="n">
-        <v>0.838988074179233</v>
+        <v>0.959518775459607</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.527359562450619</v>
+        <v>0.514803382392271</v>
       </c>
       <c r="E8" t="n">
-        <v>2.23790898284533</v>
+        <v>2.16509048993101</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0433641859175504</v>
+        <v>0.0495700846008223</v>
       </c>
       <c r="G8" t="n">
-        <v>0.187911472309385</v>
+        <v>0.278310804433051</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.581171762700682</v>
+        <v>0.238567421108613</v>
       </c>
       <c r="E9" t="n">
-        <v>2.57494928221318</v>
+        <v>0.88574204092103</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0230764196482022</v>
+        <v>0.391846434815954</v>
       </c>
       <c r="G9" t="n">
-        <v>0.149996727713314</v>
+        <v>0.622628985316801</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.148880420691841</v>
+        <v>-0.0484309802250568</v>
       </c>
       <c r="E10" t="n">
-        <v>0.542845895878518</v>
+        <v>-0.174825534769435</v>
       </c>
       <c r="F10" t="n">
-        <v>0.596420654659973</v>
+        <v>0.863910158191933</v>
       </c>
       <c r="G10" t="n">
-        <v>0.787016427137207</v>
+        <v>0.950301174011126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.304935801417024</v>
+        <v>-0.439466302042182</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.15444450153751</v>
+        <v>-1.76398805919817</v>
       </c>
       <c r="F11" t="n">
-        <v>0.269099141997596</v>
+        <v>0.101203928884746</v>
       </c>
       <c r="G11" t="n">
-        <v>0.583048140994791</v>
+        <v>0.278310804433051</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.24394864113362</v>
+        <v>0.120180580558474</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.90697059149668</v>
+        <v>0.436480837845453</v>
       </c>
       <c r="F12" t="n">
-        <v>0.380926875394842</v>
+        <v>0.669649468567247</v>
       </c>
       <c r="G12" t="n">
-        <v>0.707435625733277</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.419735161950492</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.66736327633235</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.119337538270346</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.387846999378624</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.14529294067517</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.52947962495928</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.605397251644005</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.787016427137207</v>
+        <v>0.81846046158219</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.204846311898543</v>
+        <v>-0.182819826748162</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.724982305773377</v>
+        <v>-0.644162898964507</v>
       </c>
       <c r="F2" t="n">
-        <v>0.482361053850272</v>
+        <v>0.531589787068564</v>
       </c>
       <c r="G2" t="n">
-        <v>0.783836712506691</v>
+        <v>0.76627806073437</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.295154901015106</v>
+        <v>0.420705866372277</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.07012109002528</v>
+        <v>1.60645120554253</v>
       </c>
       <c r="F3" t="n">
-        <v>0.305617440440282</v>
+        <v>0.134152695094191</v>
       </c>
       <c r="G3" t="n">
-        <v>0.783836712506691</v>
+        <v>0.737839823018051</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.488987970338459</v>
+        <v>-0.22026485150381</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.9419034872851</v>
+        <v>-0.782231348951682</v>
       </c>
       <c r="F4" t="n">
-        <v>0.075991858221109</v>
+        <v>0.449239070749437</v>
       </c>
       <c r="G4" t="n">
-        <v>0.728854142225238</v>
+        <v>0.76627806073437</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.44052970300762</v>
+        <v>-0.118943019812057</v>
       </c>
       <c r="E5" t="n">
-        <v>1.69987189469006</v>
+        <v>-0.414976591963709</v>
       </c>
       <c r="F5" t="n">
-        <v>0.114904490247227</v>
+        <v>0.685481981280161</v>
       </c>
       <c r="G5" t="n">
-        <v>0.728854142225238</v>
+        <v>0.76627806073437</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.389868787161744</v>
+        <v>-0.350221113891058</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.46659624119528</v>
+        <v>-1.29523240961749</v>
       </c>
       <c r="F6" t="n">
-        <v>0.168197109744286</v>
+        <v>0.219604016902714</v>
       </c>
       <c r="G6" t="n">
-        <v>0.728854142225238</v>
+        <v>0.76627806073437</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.235683391109077</v>
+        <v>-0.169603935657934</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.840096834280501</v>
+        <v>-0.596162284276396</v>
       </c>
       <c r="F7" t="n">
-        <v>0.417278362232276</v>
+        <v>0.562143985475688</v>
       </c>
       <c r="G7" t="n">
-        <v>0.783836712506691</v>
+        <v>0.76627806073437</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0682821039661811</v>
+        <v>0.160793341597781</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.237089500848308</v>
+        <v>0.564347712691896</v>
       </c>
       <c r="F8" t="n">
-        <v>0.816586559149225</v>
+        <v>0.582912376280973</v>
       </c>
       <c r="G8" t="n">
-        <v>0.958278064313914</v>
+        <v>0.76627806073437</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0154185396052667</v>
+        <v>0.066079455451143</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0534177378629159</v>
+        <v>0.22940734925225</v>
       </c>
       <c r="F9" t="n">
-        <v>0.958278064313914</v>
+        <v>0.822415840592361</v>
       </c>
       <c r="G9" t="n">
-        <v>0.958278064313914</v>
+        <v>0.822415840592361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0396476732706858</v>
+        <v>0.136564207932362</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.137451644233103</v>
+        <v>0.477546318929648</v>
       </c>
       <c r="F10" t="n">
-        <v>0.892953166585476</v>
+        <v>0.64155352404022</v>
       </c>
       <c r="G10" t="n">
-        <v>0.958278064313914</v>
+        <v>0.76627806073437</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.169603935657934</v>
+        <v>0.114537722781981</v>
       </c>
       <c r="E11" t="n">
-        <v>0.596162284276396</v>
+        <v>0.399398794051085</v>
       </c>
       <c r="F11" t="n">
-        <v>0.562143985475688</v>
+        <v>0.696616418849427</v>
       </c>
       <c r="G11" t="n">
-        <v>0.811985756798217</v>
+        <v>0.76627806073437</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.30176284656022</v>
+        <v>-0.55727007430464</v>
       </c>
       <c r="E12" t="n">
-        <v>1.09645036811242</v>
+        <v>-2.32490352866603</v>
       </c>
       <c r="F12" t="n">
-        <v>0.294398172808173</v>
+        <v>0.0384240248394354</v>
       </c>
       <c r="G12" t="n">
-        <v>0.783836712506691</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0704847524812193</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.244775135704207</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.810766079433868</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.958278064313914</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.218062202988772</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.774016433630803</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.453900812205413</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.783836712506691</v>
+        <v>0.42266427323379</v>
       </c>
     </row>
   </sheetData>
@@ -2454,45 +2172,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2501,76 +2219,76 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.125</v>
+        <v>0.139285714285714</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.218062202988772</v>
+        <v>0.169603935657934</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.24394864113362</v>
+        <v>0.238567421108613</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2579,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.178571428571429</v>
+        <v>0.196428571428571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,33 +2323,33 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.153571428571429</v>
+        <v>0.110714285714286</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.35</v>
+        <v>0.303571428571428</v>
       </c>
     </row>
   </sheetData>
